--- a/plantillas/Plantilla_Base_Grupo.xlsx
+++ b/plantillas/Plantilla_Base_Grupo.xlsx
@@ -10,6 +10,8 @@
     <sheet name="EJES_2026" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="EMPRESAS" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="CONFIG_DRIVE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="EQUIPO" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ACCESOS" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -451,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +470,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -553,9 +554,32 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>EQUIPO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quiénes facilitan el grupo (se ve al pie del menú).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ACCESOS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Emails habilitados a crear cuenta en el sitio. Si está vacía, cualquiera puede registrarse (y queda pendiente de autorización).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Cómo conectarla: subí este archivo a Drive, compartilo (Lector) con la cuenta de servicio del sitio, y pegá su ID en Configuración → Fuentes de datos.</t>
         </is>
@@ -572,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -684,7 +708,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>grupo_descripcion</t>
+          <t>grupo_tipo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -697,19 +721,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Descripción</t>
+          <t>Tipo de espacio</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Descripción del grupo…</t>
+          <t>Directorio Colaborativo</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>grupo_inicio</t>
+          <t>grupo_etiqueta</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -722,19 +746,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Inicio</t>
+          <t>Etiqueta del menú</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>Grupo IV · Simpleza</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>grupo_nombre_desde</t>
+          <t>facilitado_por</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -747,99 +771,99 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nombre desde</t>
+          <t>Facilitado por</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Simpleza</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>objetivo_general</t>
+          <t>grupo_descripcion</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Objetivos</t>
+          <t>Identidad</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Objetivo general</t>
+          <t>Descripción</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>Descripción del grupo…</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>objetivo_2026</t>
+          <t>grupo_inicio</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Objetivos</t>
+          <t>Identidad</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Objetivo 2026</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>2021</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>objetivo_2026_ampliado</t>
+          <t>grupo_nombre_desde</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Objetivos</t>
+          <t>Identidad</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Objetivo 2026 ampliado</t>
+          <t>Nombre desde</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>…</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>principio_01</t>
+          <t>objetivo_general</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Principios</t>
+          <t>Objetivos</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -847,24 +871,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Principio</t>
+          <t>Objetivo general</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Primer principio.</t>
+          <t>…</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>principio_02</t>
+          <t>objetivo_2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Principios</t>
+          <t>Objetivos</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -872,37 +896,182 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Principio</t>
+          <t>Objetivo 2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Segundo principio.</t>
+          <t>…</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>objetivo_2026_ampliado</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Objetivos</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Objetivo 2026 ampliado</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>principio_01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Principios</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Principio</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Primer principio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>principio_02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Principios</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Principio</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Segundo principio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>frase_destacada</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C17" t="n">
         <v>1</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Frase destacada</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Frase de cierre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>objetivo_anio_titulo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Objetivos</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Título de la tarjeta del objetivo del año</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Objetivo 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ejes_titulo</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Objetivos</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Título de la sección de ejes</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ejes temáticos 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>grupo_logo_url</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Identidad</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Logo del grupo (URL de imagen)</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1084,7 +1253,6 @@
           <t>Congreso Aapresid</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>Rosario</t>
@@ -1107,8 +1275,6 @@
           <t>Viaje Grupo El Faro: Laboulaye – Buenos Aires</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -1136,7 +1302,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1280,7 +1445,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>recorrido_en_el_faro</t>
+          <t>recorrido_en_el_grupo</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1434,4 +1599,166 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EQUIPO — Quiénes facilitan o coordinan el grupo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Se muestra al pie del menú lateral. Una fila por persona.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rol</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>mostrar_en_web</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nombre y Apellido</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Coordinadora del grupo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nombre y Apellido</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Co-facilitador</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ACCESOS — Quiénes pueden crear una cuenta en el sitio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Una cuenta por empresa. Si esta pestaña tiene filas, SOLO estos emails pueden registrarse: cualquier otro rebota. Igual, la coordinación tiene que autorizar cada cuenta antes del primer ingreso (Configuración → Quién puede entrar). Esta lista nunca se muestra en el sitio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>empresa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>contacto@empresa-uno.com</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Empresa Uno S.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Nombre del referente</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>La comparte con su equipo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/plantillas/Plantilla_Base_Grupo.xlsx
+++ b/plantillas/Plantilla_Base_Grupo.xlsx
@@ -596,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1052,26 +1052,6 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>Ejes temáticos 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>grupo_logo_url</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Identidad</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>9</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Logo del grupo (URL de imagen)</t>
         </is>
       </c>
     </row>

--- a/plantillas/Plantilla_Base_Grupo.xlsx
+++ b/plantillas/Plantilla_Base_Grupo.xlsx
@@ -710,7 +710,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Las reuniones fijadas (📌) y las marcadas como «Flexible» en el sitio no se tocan nunca.</t>
+          <t>Las reuniones fijadas (📌) y las marcadas como «Flexible» en el sitio no se modifican.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Si la fecha cae en feriado y CALENDARIO dice saltar_feriados = TRUE, queda «Feriado».</t>
+          <t>Si la fecha cae en feriado y saltar_feriados = TRUE, queda «Feriado».</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Si toca ronda de novedades o técnica según CALENDARIO, se asigna esa.</t>
+          <t>Presenta la empresa ACTIVA que hace más tiempo que no presenta, si superó semanas_entre_presentaciones y está DISPONIBLE esa fecha.</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Si no, presenta la empresa ACTIVA que hace más tiempo que no presenta y que esté DISPONIBLE esa fecha.</t>
+          <t>Si ninguna empresa corresponde, la fecha se completa con ronda de novedades o reunión técnica según la proporción configurada.</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Si ninguna empresa está disponible, la fecha queda «Flexible» y el sitio te avisa cuál fue.</t>
+          <t>Si no hay proporciones cargadas, la fecha queda «Flexible».</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>1 = todas las semanas. 2 = una semana sí y una no. 3 = cada tres semanas.</t>
+          <t>1 = hay encuentro todas las semanas. 2 = una semana de por medio. 3 = cada tres semanas.</t>
         </is>
       </c>
     </row>
@@ -1812,37 +1812,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>TRUE = si cae feriado no hay reunión. FALSE = se reúnen igual.</t>
+          <t>TRUE = si la fecha cae feriado no hay reunión. FALSE = se sesiona igual.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>ronda_novedades_cada</t>
+          <t>semanas_entre_presentaciones</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Cada cuántas reuniones va una ronda de novedades. 0 = nunca automáticamente.</t>
+          <t>Mínimo de semanas entre dos presentaciones de la misma empresa. Con 26, cada empresa presenta unas dos veces al año; las fechas que quedan libres se completan con ronda de novedades y reuniones técnicas, según las proporciones de abajo.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>tecnica_cada</t>
+          <t>proporcion_ronda_novedades</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Cada cuántas reuniones va una reunión técnica. 0 = nunca automáticamente.</t>
+          <t>Proporción de las fechas libres destinadas a ronda de novedades.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>proporcion_tecnica</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Proporción destinada a reunión técnica. Con 1 y 2, de cada tres fechas libres una es ronda y dos son técnicas. Con 0 y 0, quedan como Flexible.</t>
         </is>
       </c>
     </row>
